--- a/Excel/商店表.xlsx
+++ b/Excel/商店表.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>red armchair</t>
+          <t>红色扶手椅</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -516,7 +516,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>floor lamp</t>
+          <t>落地灯</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -534,7 +534,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>decorated bookcase</t>
+          <t>装饰书柜</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>wood coffee table</t>
+          <t>木质茶几</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -570,7 +570,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>blue pedestal table</t>
+          <t>蓝色圆柱桌</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -588,7 +588,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hanging plant 1</t>
+          <t>悬挂绿植·壹</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hanging plant 2</t>
+          <t>悬挂绿植·贰</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -624,7 +624,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hanging plant 4</t>
+          <t>悬挂绿植·肆</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -642,7 +642,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>open cardboard box</t>
+          <t>敞口纸箱</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -660,7 +660,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>closed cardboard box</t>
+          <t>封口纸箱</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>potted monstera 1</t>
+          <t>龟背竹盆栽·壹</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>potted monstera 2</t>
+          <t>龟背竹盆栽·贰</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mountain poster</t>
+          <t>山景海报</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -732,7 +732,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>wall clock</t>
+          <t>挂钟</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>wall calendar</t>
+          <t>挂历</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -768,7 +768,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>green tag</t>
+          <t>绿色挂签</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>purple tag</t>
+          <t>紫色挂签</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hanging plant</t>
+          <t>悬挂绿植</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -822,7 +822,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>blue sofa</t>
+          <t>蓝色沙发</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>open cardboard box</t>
+          <t>敞口纸箱·大</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -858,7 +858,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>book file holder</t>
+          <t>书立文件架</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -876,7 +876,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>round pod chair</t>
+          <t>圆形太空椅</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>organic wall mirror</t>
+          <t>云形壁镜</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>orb floor lamp</t>
+          <t>圆球落地灯</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -930,7 +930,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jellyfish aquarium console</t>
+          <t>水母缸边柜</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -948,7 +948,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>lava lamp</t>
+          <t>熔岩灯</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>retro dining set</t>
+          <t>复古餐桌椅</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -984,7 +984,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>cactus lamp</t>
+          <t>仙人掌灯</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>round bar shelf</t>
+          <t>圆形吧台架</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>potted palm</t>
+          <t>棕榈盆栽</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>blue beanbag</t>
+          <t>蓝色懒人沙发</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>space rug</t>
+          <t>太空地毯</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>cloud coffee table</t>
+          <t>云朵茶几</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>glass media console</t>
+          <t>玻璃电视柜</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>crescent aquarium lamp</t>
+          <t>月牙水族灯</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>retro space tv</t>
+          <t>复古太空电视</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>lava lamp</t>
+          <t>熔岩灯·高</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tall bubble aquarium</t>
+          <t>高筒气泡水族箱</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>washing machine</t>
+          <t>洗衣机</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>bathtub table set</t>
+          <t>浴缸茶座</t>
         </is>
       </c>
       <c r="C42" t="n">

--- a/Excel/商店表.xlsx
+++ b/Excel/商店表.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="商店" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="分类" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -493,16 +494,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>table_lamp_01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>红色扶手椅</t>
+          <t>台灯·01</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -511,16 +512,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>table_lamp_02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>落地灯</t>
+          <t>台灯·02</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -529,16 +530,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>table_lamp_03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>装饰书柜</t>
+          <t>台灯·03</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -547,16 +548,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>table_lamp_04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>木质茶几</t>
+          <t>台灯·04</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -565,16 +566,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>table_lamp_05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>蓝色圆柱桌</t>
+          <t>台灯·05</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -583,16 +584,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>table_lamp_06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>悬挂绿植·壹</t>
+          <t>台灯·06</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -601,16 +602,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>round_table_01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>悬挂绿植·贰</t>
+          <t>圆桌·01</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -619,16 +620,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>round_table_02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>悬挂绿植·肆</t>
+          <t>圆桌·02</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -637,16 +638,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>round_table_03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>敞口纸箱</t>
+          <t>圆桌·03</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -655,16 +656,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>round_table_04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>封口纸箱</t>
+          <t>圆桌·04</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -673,16 +674,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>round_table_05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>龟背竹盆栽·壹</t>
+          <t>圆桌·05</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -691,16 +692,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>round_table_06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>龟背竹盆栽·贰</t>
+          <t>圆桌·06</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -709,16 +710,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>round_table_07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>山景海报</t>
+          <t>圆桌·07</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -727,16 +728,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>round_table_08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>挂钟</t>
+          <t>圆桌·08</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -745,16 +746,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>crescent_aquarium_01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>挂历</t>
+          <t>月牙鱼缸·01</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -763,16 +764,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>crescent_aquarium_04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>绿色挂签</t>
+          <t>月牙鱼缸·04</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>380</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -781,16 +782,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>crescent_aquarium_05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>紫色挂签</t>
+          <t>月牙鱼缸·05</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>380</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -799,16 +800,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>023</t>
+          <t>crescent_aquarium_07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>悬挂绿植</t>
+          <t>月牙鱼缸·07</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -817,12 +818,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>cat_sofa_01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>蓝色沙发</t>
+          <t>猫耳懒人沙发·01</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -835,16 +836,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>032</t>
+          <t>cat_sofa_02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>敞口纸箱·大</t>
+          <t>猫耳懒人沙发·02</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -853,16 +854,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>cat_sofa_03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>书立文件架</t>
+          <t>猫耳懒人沙发·03</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -871,16 +872,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>036</t>
+          <t>cat_sofa_04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>圆形太空椅</t>
+          <t>猫耳懒人沙发·04</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -889,16 +890,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>037</t>
+          <t>cat_sofa_05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>云形壁镜</t>
+          <t>猫耳懒人沙发·05</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -907,16 +908,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>038</t>
+          <t>cat_sofa_06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>圆球落地灯</t>
+          <t>猫耳懒人沙发·06</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -925,16 +926,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>040</t>
+          <t>cat_sofa_07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>水母缸边柜</t>
+          <t>猫耳懒人沙发·07</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -943,16 +944,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>cat_sofa_08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>熔岩灯</t>
+          <t>猫耳懒人沙发·08</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -961,12 +962,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>single_sofa_02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>复古餐桌椅</t>
+          <t>单人沙发·02</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -979,16 +980,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>049</t>
+          <t>single_sofa_03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>仙人掌灯</t>
+          <t>单人沙发·03</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -997,16 +998,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>051</t>
+          <t>single_sofa_04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>圆形吧台架</t>
+          <t>单人沙发·04</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1015,16 +1016,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>053</t>
+          <t>single_sofa_05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>棕榈盆栽</t>
+          <t>单人沙发·05</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1033,16 +1034,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>single_sofa_06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>蓝色懒人沙发</t>
+          <t>单人沙发·06</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1051,16 +1052,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>055</t>
+          <t>single_sofa_07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>太空地毯</t>
+          <t>单人沙发·07</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1069,16 +1070,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>single_sofa_08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>云朵茶几</t>
+          <t>单人沙发·08</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1087,16 +1088,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>057</t>
+          <t>single_sofa_09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>玻璃电视柜</t>
+          <t>单人沙发·09</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1105,16 +1106,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>059</t>
+          <t>single_sofa_10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>月牙水族灯</t>
+          <t>单人沙发·10</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1123,16 +1124,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>single_sofa_11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>复古太空电视</t>
+          <t>单人沙发·11</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>140</v>
+        <v>400</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1141,16 +1142,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>single_sofa_12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>熔岩灯·高</t>
+          <t>单人沙发·12</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1159,16 +1160,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>armchair_01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>高筒气泡水族箱</t>
+          <t>扶手椅·01</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1177,16 +1178,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>075</t>
+          <t>cactus_lamp_04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>洗衣机</t>
+          <t>仙人掌灯·04</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1195,19 +1196,1579 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>077</t>
+          <t>cactus_lamp_05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>浴缸茶座</t>
+          <t>仙人掌灯·05</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>600</v>
+        <v>180</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cactus_lamp_06</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>仙人掌灯·06</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>180</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cactus_lamp_07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>仙人掌灯·07</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>180</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cactus_lamp_08</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>仙人掌灯·08</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>180</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>hanging_plant_01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>悬挂绿植·01</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>hanging_plant_03</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>悬挂绿植·03</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>140</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>hanging_plant_06</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>悬挂绿植·06</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>140</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>hanging_plant_07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>悬挂绿植·07</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>140</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>hanging_plant_08</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>悬挂绿植·08</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>140</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>hanging_plant_09</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>悬挂绿植·09</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>140</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>hanging_plant_11</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>悬挂绿植·11</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>140</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>hanging_plant_12</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>悬挂绿植·12</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>140</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>hanging_plant_13</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>悬挂绿植·13</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>140</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>hanging_plant_14</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>悬挂绿植·14</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>140</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>hanging_plant_15</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>悬挂绿植·15</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>140</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>hanging_plant_16</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>悬挂绿植·16</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>140</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>hanging_plant_17</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>悬挂绿植·17</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>140</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>hanging_plant_18</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>悬挂绿植·18</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>140</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>hanging_plant_21</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>悬挂绿植·21</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>140</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>hanging_plant_22</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>悬挂绿植·22</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>140</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>hanging_plant_23</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>悬挂绿植·23</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>140</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>hanging_plant_24</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>悬挂绿植·24</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>140</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>hanging_plant_30</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>悬挂绿植·30</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>140</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>hanging_plant_31</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>悬挂绿植·31</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>140</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>hanging_plant_32</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>悬挂绿植·32</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>140</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>hanging_plant_36</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>悬挂绿植·36</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>140</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>landscape_poster_02</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>风景海报·02</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>landscape_poster_03</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>风景海报·03</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>landscape_poster_04</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>风景海报·04</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>100</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>landscape_poster_05</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>风景海报·05</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>100</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>landscape_poster_06</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>风景海报·06</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>100</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>landscape_poster_07</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>风景海报·07</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>100</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>landscape_poster_08</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>风景海报·08</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>100</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>landscape_poster_09</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>风景海报·09</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>100</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>lava_lamp_01</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>熔岩灯·01</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>180</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>lava_lamp_02</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>熔岩灯·02</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>180</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>lava_lamp_03</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>熔岩灯·03</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>180</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>lava_lamp_04</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>熔岩灯·04</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>180</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>lava_lamp_05</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>熔岩灯·05</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>180</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>lava_lamp_06</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>熔岩灯·06</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>180</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>lava_lamp_07</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>熔岩灯·07</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>180</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>lava_lamp_08</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>熔岩灯·08</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>180</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>monstera_01</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>龟背竹·01</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>monstera_02</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>龟背竹·02</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>200</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>monstera_03</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>龟背竹·03</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>200</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>monstera_04</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>龟背竹·04</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>200</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>monstera_05</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>龟背竹·05</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>200</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>monstera_06</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>龟背竹·06</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>200</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>monstera_08</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>龟背竹·08</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>200</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>orb_decoration_01</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>球形摆件·01</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>140</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>orb_decoration_02</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>球形摆件·02</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>140</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>orb_decoration_03</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>球形摆件·03</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>140</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>orb_decoration_04</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>球形摆件·04</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>140</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>orb_decoration_05</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>球形摆件·05</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>140</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>orb_decoration_06</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>球形摆件·06</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>140</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>orb_decoration_07</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>球形摆件·07</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>140</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>orb_decoration_08</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>球形摆件·08</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>140</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>orb_decoration_09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>球形摆件·09</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>140</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>potted_plant_01</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>盆栽植物·01</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>potted_plant_02</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>盆栽植物·02</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>potted_plant_03</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>盆栽植物·03</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>150</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>potted_plant_04</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>盆栽植物·04</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>150</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>potted_plant_06</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>盆栽植物·06</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>150</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>round_rug_01</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>圆形地毯·01</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>160</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>round_rug_02</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>圆形地毯·02</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>160</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>round_rug_03</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>圆形地毯·03</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>160</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>round_rug_04</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>圆形地毯·04</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>160</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>round_rug_05</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>圆形地毯·05</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>160</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>round_rug_06</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>圆形地毯·06</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>160</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>round_rug_07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>圆形地毯·07</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>160</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>round_rug_08</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>圆形地毯·08</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>160</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>round_rug_09</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>圆形地毯·09</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>160</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>round_rug_10</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>圆形地毯·10</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>160</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>vintage_square_clock_02</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>复古方钟·02</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>vintage_square_clock_03</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>复古方钟·03</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>vintage_square_clock_04</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>复古方钟·04</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>120</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>vintage_square_clock_05</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>复古方钟·05</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>120</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>vintage_square_clock_06</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>复古方钟·06</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>120</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>vintage_square_clock_07</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>复古方钟·07</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>120</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>vintage_square_clock_08</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>复古方钟·08</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>120</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>vintage_square_clock_10</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>复古方钟·10</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>120</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>vintage_square_clock_11</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>复古方钟·11</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>120</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>分类名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>盆栽</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>绿意是屋子的呼吸，也是访客的话题。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>摆件</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>小小的物件，撑起大大的氛围。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>桌椅</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>坐下来，故事才会开始。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>壁挂</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>墙上的东西，替你说出品味。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>灯具</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>一盏灯，决定一间屋子的夜晚。</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Excel/商店表.xlsx
+++ b/Excel/商店表.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="39.125" customWidth="1" min="1" max="1"/>
@@ -2876,6 +2876,222 @@
         <v>420</v>
       </c>
       <c r="D134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>vanity_01</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>彩色梳妆台·01</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>100</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>retro_radio_01</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>复古收音机·01</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>100</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>music_player_01</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>音乐播放器·01</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>100</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>piano_01</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>奶油钢琴·01</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>100</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>flashlight_01</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>手电筒·01</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>100</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>iron_01</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>复古熨斗·01</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>100</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>telescope_01</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>复古望远镜·01</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>100</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>colorful_cabinet_01</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>彩色柜子·01</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>100</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>floor_lamp_01</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>艺术落地灯·01</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>100</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>chalkboard_01</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>复古黑板·01</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>100</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>macaron_sofa_01</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>马卡龙沙发·01</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>100</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>metronome_01</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>节拍器·01</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>100</v>
+      </c>
+      <c r="D146" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Excel/商店表.xlsx
+++ b/Excel/商店表.xlsx
@@ -518,7 +518,7 @@
         <v>150</v>
       </c>
       <c r="D3" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>150</v>
       </c>
       <c r="D4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -554,7 +554,7 @@
         <v>150</v>
       </c>
       <c r="D5" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -572,7 +572,7 @@
         <v>150</v>
       </c>
       <c r="D6" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>150</v>
       </c>
       <c r="D7" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -608,7 +608,7 @@
         <v>150</v>
       </c>
       <c r="D8" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -770,7 +770,7 @@
         <v>380</v>
       </c>
       <c r="D17" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -788,7 +788,7 @@
         <v>380</v>
       </c>
       <c r="D18" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -806,7 +806,7 @@
         <v>380</v>
       </c>
       <c r="D19" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -824,7 +824,7 @@
         <v>380</v>
       </c>
       <c r="D20" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1202,7 +1202,7 @@
         <v>180</v>
       </c>
       <c r="D41" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -1220,7 +1220,7 @@
         <v>180</v>
       </c>
       <c r="D42" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
@@ -1238,7 +1238,7 @@
         <v>180</v>
       </c>
       <c r="D43" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -1256,7 +1256,7 @@
         <v>180</v>
       </c>
       <c r="D44" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -1274,7 +1274,7 @@
         <v>180</v>
       </c>
       <c r="D45" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46">
@@ -1382,7 +1382,7 @@
         <v>140</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
@@ -1400,7 +1400,7 @@
         <v>140</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
@@ -1418,7 +1418,7 @@
         <v>140</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54">
@@ -1436,7 +1436,7 @@
         <v>140</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55">
@@ -1454,7 +1454,7 @@
         <v>140</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56">
@@ -1472,7 +1472,7 @@
         <v>140</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57">
@@ -1490,7 +1490,7 @@
         <v>140</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58">
@@ -1508,7 +1508,7 @@
         <v>140</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59">
@@ -1526,7 +1526,7 @@
         <v>140</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60">
@@ -1544,7 +1544,7 @@
         <v>140</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61">
@@ -1562,7 +1562,7 @@
         <v>140</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62">
@@ -1580,7 +1580,7 @@
         <v>140</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
@@ -1598,7 +1598,7 @@
         <v>140</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
@@ -1616,7 +1616,7 @@
         <v>140</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
@@ -1634,7 +1634,7 @@
         <v>140</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66">
@@ -1652,7 +1652,7 @@
         <v>140</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67">
@@ -1670,7 +1670,7 @@
         <v>140</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
@@ -1832,7 +1832,7 @@
         <v>180</v>
       </c>
       <c r="D76" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77">
@@ -1850,7 +1850,7 @@
         <v>180</v>
       </c>
       <c r="D77" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78">
@@ -1868,7 +1868,7 @@
         <v>180</v>
       </c>
       <c r="D78" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79">
@@ -1886,7 +1886,7 @@
         <v>180</v>
       </c>
       <c r="D79" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80">
@@ -1904,7 +1904,7 @@
         <v>180</v>
       </c>
       <c r="D80" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81">
@@ -1922,7 +1922,7 @@
         <v>180</v>
       </c>
       <c r="D81" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="82">
@@ -1940,7 +1940,7 @@
         <v>180</v>
       </c>
       <c r="D82" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83">
@@ -1958,7 +1958,7 @@
         <v>180</v>
       </c>
       <c r="D83" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84">
@@ -2030,7 +2030,7 @@
         <v>200</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88">
@@ -2048,7 +2048,7 @@
         <v>200</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89">
@@ -2066,7 +2066,7 @@
         <v>200</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90">
@@ -2084,7 +2084,7 @@
         <v>200</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91">
@@ -2102,7 +2102,7 @@
         <v>140</v>
       </c>
       <c r="D91" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2120,7 +2120,7 @@
         <v>140</v>
       </c>
       <c r="D92" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2138,7 +2138,7 @@
         <v>140</v>
       </c>
       <c r="D93" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2156,7 +2156,7 @@
         <v>140</v>
       </c>
       <c r="D94" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2174,7 +2174,7 @@
         <v>140</v>
       </c>
       <c r="D95" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2192,7 +2192,7 @@
         <v>140</v>
       </c>
       <c r="D96" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="97">
@@ -2210,7 +2210,7 @@
         <v>140</v>
       </c>
       <c r="D97" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="98">
@@ -2228,7 +2228,7 @@
         <v>140</v>
       </c>
       <c r="D98" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="99">
@@ -2246,7 +2246,7 @@
         <v>150</v>
       </c>
       <c r="D99" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100">
@@ -2264,7 +2264,7 @@
         <v>150</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101">
@@ -2282,7 +2282,7 @@
         <v>150</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102">
@@ -2300,7 +2300,7 @@
         <v>150</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103">
@@ -2318,7 +2318,7 @@
         <v>150</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="104">
@@ -2336,7 +2336,7 @@
         <v>150</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="105">
@@ -2354,7 +2354,7 @@
         <v>160</v>
       </c>
       <c r="D105" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2372,7 +2372,7 @@
         <v>160</v>
       </c>
       <c r="D106" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -2390,7 +2390,7 @@
         <v>160</v>
       </c>
       <c r="D107" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2408,7 +2408,7 @@
         <v>160</v>
       </c>
       <c r="D108" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2426,7 +2426,7 @@
         <v>160</v>
       </c>
       <c r="D109" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2444,7 +2444,7 @@
         <v>160</v>
       </c>
       <c r="D110" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111">
@@ -2462,7 +2462,7 @@
         <v>160</v>
       </c>
       <c r="D111" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="112">
@@ -2480,7 +2480,7 @@
         <v>160</v>
       </c>
       <c r="D112" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="113">
@@ -2498,7 +2498,7 @@
         <v>160</v>
       </c>
       <c r="D113" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="114">
@@ -2516,7 +2516,7 @@
         <v>160</v>
       </c>
       <c r="D114" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115">
@@ -2678,7 +2678,7 @@
         <v>120</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="124">

--- a/Excel/商店表.xlsx
+++ b/Excel/商店表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="43650" yWindow="1710" windowWidth="28800" windowHeight="15510" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="商店" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="分类" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商店" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -608,7 +608,7 @@
         <v>150</v>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -1202,7 +1202,7 @@
         <v>180</v>
       </c>
       <c r="D41" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42">
@@ -1220,7 +1220,7 @@
         <v>180</v>
       </c>
       <c r="D42" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
@@ -1238,7 +1238,7 @@
         <v>180</v>
       </c>
       <c r="D43" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44">
@@ -1256,7 +1256,7 @@
         <v>180</v>
       </c>
       <c r="D44" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45">
@@ -1274,7 +1274,7 @@
         <v>180</v>
       </c>
       <c r="D45" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
@@ -1382,7 +1382,7 @@
         <v>140</v>
       </c>
       <c r="D51" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52">
@@ -1400,7 +1400,7 @@
         <v>140</v>
       </c>
       <c r="D52" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53">
@@ -1418,7 +1418,7 @@
         <v>140</v>
       </c>
       <c r="D53" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54">
@@ -1436,7 +1436,7 @@
         <v>140</v>
       </c>
       <c r="D54" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55">
@@ -1454,7 +1454,7 @@
         <v>140</v>
       </c>
       <c r="D55" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56">
@@ -1472,7 +1472,7 @@
         <v>140</v>
       </c>
       <c r="D56" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57">
@@ -1490,7 +1490,7 @@
         <v>140</v>
       </c>
       <c r="D57" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58">
@@ -1508,7 +1508,7 @@
         <v>140</v>
       </c>
       <c r="D58" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59">
@@ -1526,7 +1526,7 @@
         <v>140</v>
       </c>
       <c r="D59" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60">
@@ -1544,7 +1544,7 @@
         <v>140</v>
       </c>
       <c r="D60" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61">
@@ -1562,7 +1562,7 @@
         <v>140</v>
       </c>
       <c r="D61" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
@@ -1580,7 +1580,7 @@
         <v>140</v>
       </c>
       <c r="D62" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63">
@@ -1598,7 +1598,7 @@
         <v>140</v>
       </c>
       <c r="D63" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64">
@@ -1616,7 +1616,7 @@
         <v>140</v>
       </c>
       <c r="D64" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65">
@@ -1634,7 +1634,7 @@
         <v>140</v>
       </c>
       <c r="D65" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66">
@@ -1652,7 +1652,7 @@
         <v>140</v>
       </c>
       <c r="D66" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67">
@@ -1670,7 +1670,7 @@
         <v>140</v>
       </c>
       <c r="D67" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68">
@@ -1832,7 +1832,7 @@
         <v>180</v>
       </c>
       <c r="D76" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77">
@@ -1850,7 +1850,7 @@
         <v>180</v>
       </c>
       <c r="D77" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78">
@@ -1868,7 +1868,7 @@
         <v>180</v>
       </c>
       <c r="D78" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79">
@@ -1886,7 +1886,7 @@
         <v>180</v>
       </c>
       <c r="D79" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
@@ -1904,7 +1904,7 @@
         <v>180</v>
       </c>
       <c r="D80" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81">
@@ -1922,7 +1922,7 @@
         <v>180</v>
       </c>
       <c r="D81" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82">
@@ -1940,7 +1940,7 @@
         <v>180</v>
       </c>
       <c r="D82" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83">
@@ -1958,7 +1958,7 @@
         <v>180</v>
       </c>
       <c r="D83" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84">
@@ -2030,7 +2030,7 @@
         <v>200</v>
       </c>
       <c r="D87" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88">
@@ -2048,7 +2048,7 @@
         <v>200</v>
       </c>
       <c r="D88" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89">
@@ -2066,7 +2066,7 @@
         <v>200</v>
       </c>
       <c r="D89" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90">
@@ -2084,7 +2084,7 @@
         <v>200</v>
       </c>
       <c r="D90" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="91">
@@ -2192,7 +2192,7 @@
         <v>140</v>
       </c>
       <c r="D96" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97">
@@ -2210,7 +2210,7 @@
         <v>140</v>
       </c>
       <c r="D97" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98">
@@ -2228,7 +2228,7 @@
         <v>140</v>
       </c>
       <c r="D98" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99">
@@ -2246,7 +2246,7 @@
         <v>150</v>
       </c>
       <c r="D99" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100">
@@ -2264,7 +2264,7 @@
         <v>150</v>
       </c>
       <c r="D100" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101">
@@ -2282,7 +2282,7 @@
         <v>150</v>
       </c>
       <c r="D101" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="102">
@@ -2300,7 +2300,7 @@
         <v>150</v>
       </c>
       <c r="D102" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103">
@@ -2318,7 +2318,7 @@
         <v>150</v>
       </c>
       <c r="D103" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104">
@@ -2336,7 +2336,7 @@
         <v>150</v>
       </c>
       <c r="D104" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105">
@@ -2444,7 +2444,7 @@
         <v>160</v>
       </c>
       <c r="D110" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111">
@@ -2462,7 +2462,7 @@
         <v>160</v>
       </c>
       <c r="D111" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112">
@@ -2480,7 +2480,7 @@
         <v>160</v>
       </c>
       <c r="D112" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="113">
@@ -2498,7 +2498,7 @@
         <v>160</v>
       </c>
       <c r="D113" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114">
@@ -2516,7 +2516,7 @@
         <v>160</v>
       </c>
       <c r="D114" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115">
@@ -2678,7 +2678,7 @@
         <v>120</v>
       </c>
       <c r="D123" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="124">
